--- a/countries/dk/2020-2025.xlsx
+++ b/countries/dk/2020-2025.xlsx
@@ -69506,17 +69506,17 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -69535,13 +69535,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="O352" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="R352" t="n">
-        <v>0.1999164682356889</v>
+        <v>0.5497702876481443</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -69550,7 +69550,7 @@
       </c>
       <c r="U352" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
+          <t>SER_DK_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -69575,7 +69575,7 @@
       </c>
       <c r="AS352" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
+          <t>SER_DK_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT352" t="n">
@@ -69665,17 +69665,17 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -69694,19 +69694,19 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="O353" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="U353" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
+          <t>SER_DK_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="V353" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
+          <t>SER_DK_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="W353" t="inlineStr">
@@ -69716,7 +69716,7 @@
       </c>
       <c r="X353" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="Y353" t="inlineStr">
@@ -69809,7 +69809,7 @@
       </c>
       <c r="AS353" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
+          <t>SER_DK_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT353" t="n">
@@ -69899,17 +69899,17 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -69928,13 +69928,13 @@
         </is>
       </c>
       <c r="N354" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O354" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R354" t="n">
-        <v>0</v>
+        <v>0.1999164682356889</v>
       </c>
       <c r="S354" t="inlineStr">
         <is>
@@ -69943,7 +69943,7 @@
       </c>
       <c r="U354" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
+          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -69968,7 +69968,7 @@
       </c>
       <c r="AS354" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
+          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT354" t="n">
@@ -70058,17 +70058,17 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -70087,19 +70087,19 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O355" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U355" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
+          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="V355" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
+          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="W355" t="inlineStr">
@@ -70109,7 +70109,7 @@
       </c>
       <c r="X355" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y355" t="inlineStr">
@@ -70202,7 +70202,7 @@
       </c>
       <c r="AS355" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
+          <t>SER_DK_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT355" t="n">
@@ -70292,22 +70292,22 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D040</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>风疹</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -70321,13 +70321,13 @@
         </is>
       </c>
       <c r="N356" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="O356" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="R356" t="n">
-        <v>3.781753190791781</v>
+        <v>0</v>
       </c>
       <c r="S356" t="inlineStr">
         <is>
@@ -70336,7 +70336,7 @@
       </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -70361,7 +70361,7 @@
       </c>
       <c r="AS356" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT356" t="n">
@@ -70451,22 +70451,22 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D040</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>风疹</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -70480,19 +70480,19 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="O357" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="V357" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="W357" t="inlineStr">
@@ -70502,7 +70502,7 @@
       </c>
       <c r="X357" t="inlineStr">
         <is>
-          <t>Legionnaires' disease</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="Y357" t="inlineStr">
@@ -70595,7 +70595,7 @@
       </c>
       <c r="AS357" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+          <t>SER_DK_ECDC_RUBE_ANNUAL</t>
         </is>
       </c>
       <c r="AT357" t="n">
@@ -70642,6 +70642,2364 @@
         </is>
       </c>
       <c r="BC357" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>5716</v>
+      </c>
+      <c r="O358" t="n">
+        <v>5716</v>
+      </c>
+      <c r="R358" t="n">
+        <v>95.22687770293312</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO358" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP358" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ358" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT358" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU358" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV358" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW358" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX358" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY358" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA358" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB358" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC358" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N359" t="n">
+        <v>5716</v>
+      </c>
+      <c r="O359" t="n">
+        <v>5716</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>SRC_DK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>country:DK:national</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ359" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK359" t="inlineStr">
+        <is>
+          <t>Denmark annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM359" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN359" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO359" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP359" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT359" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU359" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV359" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW359" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX359" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY359" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA359" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB359" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC359" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>134</v>
+      </c>
+      <c r="O360" t="n">
+        <v>134</v>
+      </c>
+      <c r="R360" t="n">
+        <v>2.232400561965192</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO360" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP360" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU360" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV360" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW360" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX360" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY360" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA360" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB360" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC360" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>134</v>
+      </c>
+      <c r="O361" t="n">
+        <v>134</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>SRC_DK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>country:DK:national</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>Denmark annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM361" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN361" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU361" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV361" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW361" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY361" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA361" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC361" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>227</v>
+      </c>
+      <c r="O362" t="n">
+        <v>227</v>
+      </c>
+      <c r="R362" t="n">
+        <v>3.781753190791781</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO362" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP362" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU362" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV362" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW362" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX362" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY362" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA362" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB362" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC362" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>227</v>
+      </c>
+      <c r="O363" t="n">
+        <v>227</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>SRC_DK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>Legionnaires' disease</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>country:DK:national</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr">
+        <is>
+          <t>Denmark annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM363" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN363" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT363" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU363" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV363" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW363" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA363" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB363" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC363" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>84</v>
+      </c>
+      <c r="O364" t="n">
+        <v>84</v>
+      </c>
+      <c r="R364" t="n">
+        <v>1.399415277649822</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV364" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW364" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC364" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>84</v>
+      </c>
+      <c r="O365" t="n">
+        <v>84</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>SRC_DK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>country:DK:national</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>Denmark annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN365" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ365" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV365" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW365" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX365" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY365" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA365" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB365" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC365" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N366" t="n">
+        <v>1051</v>
+      </c>
+      <c r="O366" t="n">
+        <v>1051</v>
+      </c>
+      <c r="R366" t="n">
+        <v>17.50935067630908</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO366" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP366" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ366" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU366" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV366" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW366" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX366" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY366" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA366" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB366" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC366" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N367" t="n">
+        <v>1051</v>
+      </c>
+      <c r="O367" t="n">
+        <v>1051</v>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>SRC_DK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>country:DK:national</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ367" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK367" t="inlineStr">
+        <is>
+          <t>Denmark annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM367" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN367" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO367" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP367" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ367" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT367" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU367" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV367" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW367" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX367" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY367" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA367" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB367" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC367" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N368" t="n">
+        <v>1050</v>
+      </c>
+      <c r="O368" t="n">
+        <v>1050</v>
+      </c>
+      <c r="R368" t="n">
+        <v>17.49269097062277</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO368" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP368" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ368" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT368" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU368" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV368" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW368" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX368" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY368" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA368" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB368" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC368" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N369" t="n">
+        <v>1050</v>
+      </c>
+      <c r="O369" t="n">
+        <v>1050</v>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>SRC_DK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>STEC/VTEC infection</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>country:DK:national</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ369" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK369" t="inlineStr">
+        <is>
+          <t>Denmark annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM369" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN369" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO369" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP369" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ369" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr">
+        <is>
+          <t>SER_DK_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT369" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU369" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV369" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW369" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX369" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY369" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA369" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB369" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC369" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -70763,7 +73121,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -70773,7 +73131,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11">
@@ -70793,7 +73151,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
@@ -70825,7 +73183,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>265010</v>
+        <v>273078</v>
       </c>
     </row>
     <row r="16">
